--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260713.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>921,244,000</t>
+          <t>172,341,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.56%</t>
+          <t>10.71%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>171,041,000</t>
+          <t>921,244,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>10.07%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>374,689,486</t>
+          <t>372,689,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.93%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>185,302,000</t>
+          <t>184,896,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.67%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,537,000</t>
+          <t>38,437,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.45%</t>
         </is>
       </c>
     </row>
@@ -721,56 +721,56 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>112,174,000</t>
+          <t>111,174,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -787,100 +787,100 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,005,000</t>
+          <t>4,975,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>25,944,000</t>
+          <t>28,330,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>31,886,000</t>
+          <t>1,928</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,857</t>
+          <t>96,642,442</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>97,242,442</t>
+          <t>25,744,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -897,100 +897,100 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>132,519,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>31,886,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>371,675,000</t>
+          <t>373,225,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1051,100 +1051,100 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>150,152,000</t>
+          <t>149,152,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>101,917,000</t>
+          <t>61,890,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,290,000</t>
+          <t>101,917,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>181,756,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>184,756,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1161,100 +1161,100 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>82,168,000</t>
+          <t>81,868,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>278,866,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>281,366,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,683,000</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>14,583,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>10,851,722,040</t>
+          <t>14,574,461,363</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,256,101,821</t>
+          <t>3,214,593,385</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-182,459,833</t>
+          <t>-115,944,618</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
